--- a/2026/maio/20260512/data/sprint_simulado.xlsx
+++ b/2026/maio/20260512/data/sprint_simulado.xlsx
@@ -2257,7 +2257,7 @@
         <v>85</v>
       </c>
       <c r="O3">
-        <v>4.9000000000000004</v>
+        <v>5.2</v>
       </c>
       <c r="P3">
         <v>195</v>
@@ -2417,7 +2417,7 @@
         <v>116</v>
       </c>
       <c r="R5">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>24</v>
@@ -2565,7 +2565,7 @@
         <v>107</v>
       </c>
       <c r="R7">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S7" s="3" t="s">
         <v>34</v>
@@ -3253,7 +3253,7 @@
         <v>95</v>
       </c>
       <c r="O17">
-        <v>4.4000000000000004</v>
+        <v>5.3</v>
       </c>
       <c r="P17">
         <v>241</v>
@@ -3463,7 +3463,7 @@
         <v>81</v>
       </c>
       <c r="O20">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="P20">
         <v>204</v>
@@ -3531,7 +3531,7 @@
         <v>122</v>
       </c>
       <c r="O21">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="P21">
         <v>152</v>
@@ -3599,7 +3599,7 @@
         <v>123</v>
       </c>
       <c r="O22">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="P22">
         <v>212</v>
@@ -4564,7 +4564,7 @@
         <v>110</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="P36">
         <v>204</v>
@@ -4635,7 +4635,7 @@
         <v>131</v>
       </c>
       <c r="O37">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="P37">
         <v>164</v>
@@ -4916,7 +4916,7 @@
         <v>151</v>
       </c>
       <c r="O41">
-        <v>4.9000000000000004</v>
+        <v>6.2</v>
       </c>
       <c r="P41">
         <v>278</v>
@@ -5554,7 +5554,7 @@
         <v>93</v>
       </c>
       <c r="R50">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>163</v>
@@ -5616,7 +5616,7 @@
         <v>133</v>
       </c>
       <c r="O51">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="P51">
         <v>166</v>
@@ -6107,7 +6107,7 @@
         <v>76</v>
       </c>
       <c r="O58">
-        <v>4.8</v>
+        <v>5.0</v>
       </c>
       <c r="P58">
         <v>163</v>
@@ -6598,7 +6598,7 @@
         <v>93</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="P65">
         <v>190</v>
@@ -7234,7 +7234,7 @@
         <v>140</v>
       </c>
       <c r="R74">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="S74" s="3" t="s">
         <v>214</v>
@@ -7435,7 +7435,7 @@
         <v>90</v>
       </c>
       <c r="O77">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P77">
         <v>179</v>
@@ -8133,7 +8133,7 @@
         <v>135</v>
       </c>
       <c r="O87">
-        <v>4.9000000000000004</v>
+        <v>5.9</v>
       </c>
       <c r="P87">
         <v>118</v>
@@ -8204,7 +8204,7 @@
         <v>76</v>
       </c>
       <c r="O88">
-        <v>4.7</v>
+        <v>5.0</v>
       </c>
       <c r="P88">
         <v>193</v>
@@ -8275,7 +8275,7 @@
         <v>108</v>
       </c>
       <c r="O89">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="P89">
         <v>225</v>
@@ -8340,7 +8340,7 @@
         <v>110</v>
       </c>
       <c r="O90">
-        <v>4.9000000000000004</v>
+        <v>5.5</v>
       </c>
       <c r="P90">
         <v>218</v>
@@ -8411,7 +8411,7 @@
         <v>105</v>
       </c>
       <c r="O91">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="P91">
         <v>131</v>
@@ -8624,7 +8624,7 @@
         <v>90</v>
       </c>
       <c r="O94">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="P94">
         <v>168</v>
@@ -8695,7 +8695,7 @@
         <v>76</v>
       </c>
       <c r="O95">
-        <v>4.8</v>
+        <v>5.0</v>
       </c>
       <c r="P95">
         <v>139</v>
@@ -8775,7 +8775,7 @@
         <v>94</v>
       </c>
       <c r="R96">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="S96" s="3" t="s">
         <v>255</v>
@@ -10283,7 +10283,7 @@
         <v>93</v>
       </c>
       <c r="O118">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="Q118">
         <v>141</v>
@@ -10703,7 +10703,7 @@
         <v>94</v>
       </c>
       <c r="O124">
-        <v>4.5999999999999996</v>
+        <v>5.3</v>
       </c>
       <c r="P124">
         <v>147</v>
@@ -10845,7 +10845,7 @@
         <v>115</v>
       </c>
       <c r="O126">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="P126">
         <v>239</v>
@@ -11333,7 +11333,7 @@
         <v>118</v>
       </c>
       <c r="O133">
-        <v>4.4000000000000004</v>
+        <v>5.6</v>
       </c>
       <c r="P133">
         <v>209</v>
@@ -11481,7 +11481,7 @@
         <v>62</v>
       </c>
       <c r="R135">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="S135" s="3" t="s">
         <v>330</v>
@@ -12306,7 +12306,7 @@
         <v>77</v>
       </c>
       <c r="R147">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="S147" s="3" t="s">
         <v>353</v>
@@ -12445,7 +12445,7 @@
         <v>91</v>
       </c>
       <c r="R149">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="S149" s="3" t="s">
         <v>357</v>
@@ -12649,7 +12649,7 @@
         <v>126</v>
       </c>
       <c r="O152">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="P152">
         <v>191</v>
@@ -12859,7 +12859,7 @@
         <v>143</v>
       </c>
       <c r="O155">
-        <v>3.9</v>
+        <v>6.0</v>
       </c>
       <c r="P155">
         <v>211</v>
@@ -13146,7 +13146,7 @@
         <v>89</v>
       </c>
       <c r="R159">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="S159" s="3" t="s">
         <v>378</v>
@@ -13835,7 +13835,7 @@
         <v>86</v>
       </c>
       <c r="O169">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="P169">
         <v>282</v>
@@ -14755,7 +14755,7 @@
         <v>108</v>
       </c>
       <c r="O182">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="P182">
         <v>287</v>
@@ -14962,7 +14962,7 @@
         <v>142</v>
       </c>
       <c r="O185">
-        <v>4.8</v>
+        <v>6.0</v>
       </c>
       <c r="P185">
         <v>173</v>
@@ -15447,7 +15447,7 @@
         <v>136</v>
       </c>
       <c r="O192">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="P192">
         <v>161</v>
